--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="26">
   <si>
     <t>Docente</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -63,6 +60,21 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>6AEV</t>
+  </si>
+  <si>
+    <t>6ALCV</t>
+  </si>
+  <si>
+    <t>6APV</t>
+  </si>
+  <si>
+    <t>6ARHV</t>
+  </si>
+  <si>
+    <t>6ASV</t>
+  </si>
+  <si>
     <t>6AEM</t>
   </si>
   <si>
@@ -79,24 +91,6 @@
   </si>
   <si>
     <t>6BLCM</t>
-  </si>
-  <si>
-    <t>6AEV</t>
-  </si>
-  <si>
-    <t>6ALCV</t>
-  </si>
-  <si>
-    <t>6APV</t>
-  </si>
-  <si>
-    <t>6ARHV</t>
-  </si>
-  <si>
-    <t>6ASV</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
   </si>
   <si>
     <t>TEMAS DE FILOSOFÍA</t>
@@ -463,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -513,21 +507,33 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="1">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.1</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -536,21 +542,33 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>65.38</v>
+      </c>
+      <c r="H3" s="1">
+        <v>34.62</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.4</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -559,21 +577,33 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G4" s="1">
+        <v>58.82</v>
+      </c>
+      <c r="H4" s="1">
+        <v>41.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5.9</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -582,97 +612,133 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G5" s="1">
+        <v>58.06</v>
+      </c>
+      <c r="H5" s="1">
+        <v>41.94</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>83.33</v>
+      </c>
+      <c r="H7" s="1">
+        <v>16.67</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.5</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>94.12</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>5.88</v>
       </c>
       <c r="I8" s="2">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -683,31 +749,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>65.38</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>34.62</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -718,31 +784,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>58.82</v>
+        <v>94.44</v>
       </c>
       <c r="H10" s="1">
-        <v>41.18</v>
+        <v>5.56</v>
       </c>
       <c r="I10" s="2">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -753,31 +819,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>31</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
       <c r="F11">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>58.06</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>41.94</v>
+        <v>14.29</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -791,240 +857,33 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>90.63</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>25</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H13" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14">
-        <v>34</v>
-      </c>
-      <c r="E14">
-        <v>32</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16">
-        <v>36</v>
-      </c>
-      <c r="E16">
-        <v>34</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>94.44</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5.56</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>28</v>
-      </c>
-      <c r="E17">
-        <v>24</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H17" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>32</v>
-      </c>
-      <c r="E18">
-        <v>29</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>90.63</v>
-      </c>
-      <c r="H18" s="1">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I18" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1035,7 +894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1085,22 +944,31 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1108,22 +976,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1131,22 +1008,31 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1154,88 +1040,115 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1244,7 +1157,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1252,22 +1165,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1276,7 +1189,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1284,22 +1197,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1308,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1316,22 +1229,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1340,7 +1253,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1351,19 +1264,19 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1372,201 +1285,9 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>30</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>30</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14">
-        <v>34</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>34</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>34</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16">
-        <v>36</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>36</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>36</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>28</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>28</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>28</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>32</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>32</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>32</v>
-      </c>
-      <c r="K18" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1577,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1627,21 +1348,33 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="1">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.6</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1650,21 +1383,33 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>65.38</v>
+      </c>
+      <c r="H3" s="1">
+        <v>34.62</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.5</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1673,21 +1418,33 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G4" s="1">
+        <v>58.82</v>
+      </c>
+      <c r="H4" s="1">
+        <v>41.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.1</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1696,97 +1453,133 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G5" s="1">
+        <v>58.06</v>
+      </c>
+      <c r="H5" s="1">
+        <v>41.94</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.1</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>83.33</v>
+      </c>
+      <c r="H7" s="1">
+        <v>16.67</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.5</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>94.12</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>5.88</v>
       </c>
       <c r="I8" s="2">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1797,31 +1590,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>65.38</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>34.62</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1832,31 +1625,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>58.82</v>
+        <v>94.44</v>
       </c>
       <c r="H10" s="1">
-        <v>41.18</v>
+        <v>5.56</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1867,31 +1660,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>31</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
       <c r="F11">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>58.06</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>41.94</v>
+        <v>14.29</v>
       </c>
       <c r="I11" s="2">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1905,240 +1698,33 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>90.63</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>25</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H13" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14">
-        <v>34</v>
-      </c>
-      <c r="E14">
-        <v>32</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16">
-        <v>36</v>
-      </c>
-      <c r="E16">
-        <v>34</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>94.44</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5.56</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>28</v>
-      </c>
-      <c r="E17">
-        <v>24</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H17" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>32</v>
-      </c>
-      <c r="E18">
-        <v>29</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>90.63</v>
-      </c>
-      <c r="H18" s="1">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I18" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
@@ -60,6 +59,12 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
     <t>6AEV</t>
   </si>
   <si>
@@ -91,9 +96,6 @@
   </si>
   <si>
     <t>6BLCM</t>
-  </si>
-  <si>
-    <t>TEMAS DE FILOSOFÍA</t>
   </si>
 </sst>
 </file>
@@ -457,11 +459,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -507,10 +509,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -545,7 +547,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>26</v>
@@ -557,10 +559,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>65.38</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>34.62</v>
+        <v>34.6</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -577,10 +579,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>17</v>
@@ -592,10 +594,10 @@
         <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>58.82</v>
+        <v>58.8</v>
       </c>
       <c r="H4" s="1">
-        <v>41.18</v>
+        <v>41.2</v>
       </c>
       <c r="I4" s="2">
         <v>5.9</v>
@@ -612,10 +614,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -627,10 +629,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="1">
-        <v>58.06</v>
+        <v>58.1</v>
       </c>
       <c r="H5" s="1">
-        <v>41.94</v>
+        <v>41.9</v>
       </c>
       <c r="I5" s="2">
         <v>6</v>
@@ -644,31 +646,25 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>56.4</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -679,31 +675,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
       <c r="E7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -714,31 +710,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -752,28 +742,28 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>25</v>
       </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
       <c r="F9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -787,28 +777,28 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>94.44</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>5.56</v>
+        <v>5.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -822,28 +812,28 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
       <c r="D11">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>85.70999999999999</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1">
-        <v>14.29</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -857,33 +847,161 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D12">
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>24</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H13" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
         <v>32</v>
       </c>
-      <c r="E12">
+      <c r="E14">
         <v>29</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>3</v>
       </c>
-      <c r="G12" s="1">
-        <v>90.63</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="G14" s="1">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="I14" s="2">
         <v>8.1</v>
       </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>180</v>
+      </c>
+      <c r="E15">
+        <v>162</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1">
+        <v>90</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>293</v>
+      </c>
+      <c r="E16">
+        <v>234</v>
+      </c>
+      <c r="F16">
+        <v>59</v>
+      </c>
+      <c r="G16" s="1">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20.1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -894,11 +1012,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -944,31 +1062,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.6</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -979,28 +1100,31 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>34.6</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.5</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1008,31 +1132,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>17</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>41.2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.1</v>
       </c>
       <c r="J4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1040,127 +1167,127 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>41.9</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.1</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>43.6</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.1</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
       <c r="E7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.9</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1168,31 +1295,34 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>25</v>
       </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
       <c r="F9">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1200,31 +1330,34 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>5.9</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1232,31 +1365,34 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
       <c r="D11">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1264,467 +1400,161 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D12">
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>24</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H13" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
         <v>32</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>32</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>100</v>
-      </c>
-      <c r="J12">
-        <v>32</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E14">
+        <v>29</v>
+      </c>
+      <c r="F14">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="G14" s="1">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>180</v>
+      </c>
+      <c r="E15">
+        <v>162</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1">
+        <v>90</v>
+      </c>
+      <c r="H15" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="I15" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1">
-        <v>40</v>
-      </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3">
-        <v>26</v>
-      </c>
-      <c r="E3">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1">
-        <v>65.38</v>
-      </c>
-      <c r="H3" s="1">
-        <v>34.62</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1">
-        <v>58.82</v>
-      </c>
-      <c r="H4" s="1">
-        <v>41.18</v>
-      </c>
-      <c r="I4" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>31</v>
-      </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1">
-        <v>58.06</v>
-      </c>
-      <c r="H5" s="1">
-        <v>41.94</v>
-      </c>
-      <c r="I5" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H7" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>34</v>
-      </c>
-      <c r="E8">
-        <v>32</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>90</v>
-      </c>
-      <c r="H9" s="1">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10">
-        <v>36</v>
-      </c>
-      <c r="E10">
-        <v>34</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" s="1">
-        <v>94.44</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5.56</v>
-      </c>
-      <c r="I10" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11">
-        <v>28</v>
-      </c>
-      <c r="E11">
-        <v>24</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H11" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I11" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>29</v>
-      </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1">
-        <v>90.63</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I12" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="D16">
+        <v>293</v>
+      </c>
+      <c r="E16">
+        <v>234</v>
+      </c>
+      <c r="F16">
+        <v>59</v>
+      </c>
+      <c r="G16" s="1">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20.1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="28">
   <si>
     <t>Docente</t>
   </si>
@@ -59,10 +59,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>6AEV</t>
@@ -463,7 +466,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -509,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -544,10 +547,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>26</v>
@@ -579,10 +582,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>17</v>
@@ -614,10 +617,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -648,6 +651,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
       <c r="D6">
         <v>94</v>
       </c>
@@ -678,10 +684,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -712,6 +718,9 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
       <c r="D8">
         <v>19</v>
       </c>
@@ -742,10 +751,10 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -777,10 +786,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>34</v>
@@ -812,10 +821,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -847,10 +856,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>36</v>
@@ -882,10 +891,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>28</v>
@@ -917,10 +926,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>32</v>
@@ -951,6 +960,9 @@
       <c r="A15" t="s">
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
       <c r="D15">
         <v>180</v>
       </c>
@@ -977,8 +989,8 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
+      <c r="B16" t="s">
+        <v>16</v>
       </c>
       <c r="D16">
         <v>293</v>
@@ -1062,10 +1074,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -1097,10 +1109,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>26</v>
@@ -1132,10 +1144,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>17</v>
@@ -1167,10 +1179,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -1201,6 +1213,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
       <c r="D6">
         <v>94</v>
       </c>
@@ -1231,10 +1246,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -1265,6 +1280,9 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
       <c r="D8">
         <v>19</v>
       </c>
@@ -1295,10 +1313,10 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -1330,10 +1348,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>34</v>
@@ -1365,10 +1383,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -1400,10 +1418,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>36</v>
@@ -1435,10 +1453,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>28</v>
@@ -1470,10 +1488,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>32</v>
@@ -1504,6 +1522,9 @@
       <c r="A15" t="s">
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
       <c r="D15">
         <v>180</v>
       </c>
@@ -1530,8 +1551,8 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
+      <c r="B16" t="s">
+        <v>16</v>
       </c>
       <c r="D16">
         <v>293</v>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="28">
   <si>
     <t>Docente</t>
   </si>
@@ -1083,6 +1084,568 @@
         <v>20</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>31</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>94</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>94</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>94</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>34</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>34</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>34</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>36</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>36</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>28</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>32</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>180</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>180</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>180</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>293</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>293</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>293</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
         <v>8</v>
       </c>
       <c r="F2">

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -1084,25 +1084,25 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1119,25 +1119,25 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1154,25 +1154,25 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1189,25 +1189,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1221,25 +1221,25 @@
         <v>94</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F6">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>61.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>38.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1323,25 +1323,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1358,25 +1358,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1393,25 +1393,25 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1428,25 +1428,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1463,25 +1463,25 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1498,25 +1498,25 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1530,25 +1530,25 @@
         <v>180</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F15">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1559,25 +1559,25 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F16">
-        <v>293</v>
+        <v>70</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>23.9</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1646,19 +1646,19 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>65.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H3" s="1">
-        <v>34.6</v>
+        <v>30.8</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1716,19 +1716,19 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>58.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>41.2</v>
+        <v>29.4</v>
       </c>
       <c r="I4" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1751,19 +1751,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="H5" s="1">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
       <c r="I5" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1783,19 +1783,19 @@
         <v>94</v>
       </c>
       <c r="E6">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
-        <v>56.4</v>
+        <v>61.7</v>
       </c>
       <c r="H6" s="1">
-        <v>43.6</v>
+        <v>38.3</v>
       </c>
       <c r="I6" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1885,19 +1885,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1920,19 +1920,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2025,16 +2025,16 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I13" s="2">
         <v>7.4</v>
@@ -2060,19 +2060,19 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H14" s="1">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         <v>180</v>
       </c>
       <c r="E15">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="H15" s="1">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2121,19 +2121,19 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F16">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G16" s="1">
-        <v>79.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -1256,25 +1256,25 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1288,25 +1288,25 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1559,25 +1559,25 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F16">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G16" s="1">
-        <v>76.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>23.9</v>
+        <v>18.1</v>
       </c>
       <c r="I16" s="2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1818,19 +1818,19 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1850,19 +1850,19 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F16">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" s="1">
-        <v>82.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="I16" s="2">
         <v>7.4</v>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -1028,8 +1028,7 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1590,8 +1589,7 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1646,19 +1644,19 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H2" s="1">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1681,19 +1679,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1716,19 +1714,19 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>70.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H4" s="1">
-        <v>29.4</v>
+        <v>11.8</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1751,19 +1749,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>61.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>38.7</v>
+        <v>12.9</v>
       </c>
       <c r="I5" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1783,19 +1781,19 @@
         <v>94</v>
       </c>
       <c r="E6">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>61.7</v>
+        <v>83</v>
       </c>
       <c r="H6" s="1">
-        <v>38.3</v>
+        <v>17</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1818,19 +1816,19 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>89.5</v>
+        <v>84.2</v>
       </c>
       <c r="H7" s="1">
-        <v>10.5</v>
+        <v>15.8</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1850,19 +1848,19 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>89.5</v>
+        <v>84.2</v>
       </c>
       <c r="H8" s="1">
-        <v>10.5</v>
+        <v>15.8</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1885,19 +1883,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1920,19 +1918,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1955,19 +1953,19 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1990,16 +1988,16 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>8.800000000000001</v>
@@ -2025,19 +2023,19 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>82.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>17.9</v>
+        <v>3.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2060,19 +2058,19 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2092,19 +2090,19 @@
         <v>180</v>
       </c>
       <c r="E15">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>91.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I15" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2121,19 +2119,19 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="F16">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G16" s="1">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="H16" s="1">
-        <v>18.1</v>
+        <v>6.8</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20222.xlsx
+++ b/academias/Humanidades - Estadisticos 20222.xlsx
@@ -2023,16 +2023,16 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
         <v>7.6</v>
@@ -2090,16 +2090,16 @@
         <v>180</v>
       </c>
       <c r="E15">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>8.199999999999999</v>
@@ -2119,16 +2119,16 @@
         <v>293</v>
       </c>
       <c r="E16">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="H16" s="1">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="I16" s="2">
         <v>7.5</v>
